--- a/data/dividends_info_20260427.xlsx
+++ b/data/dividends_info_20260427.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.38000106811523</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2074688745596896</v>
+        <v>0.2123643174414921</v>
       </c>
       <c r="J2" t="n">
         <v>322</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.79999923706055</v>
+        <v>56.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.254480303890547</v>
+        <v>1.244444444444444</v>
       </c>
       <c r="J3" t="n">
         <v>301</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.399999618530273</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6329114229666515</v>
       </c>
       <c r="J4" t="n">
         <v>231</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J5" t="n">
         <v>231</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.32500076293945</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2077322525450171</v>
+        <v>0.2123643174414921</v>
       </c>
       <c r="J6" t="n">
         <v>231</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I8" t="n">
-        <v>3.333333333333333</v>
+        <v>3.367003334568775</v>
       </c>
       <c r="J8" t="n">
         <v>203</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.699999809265137</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I9" t="n">
-        <v>1.052631614170798</v>
+        <v>1.034482724601393</v>
       </c>
       <c r="J9" t="n">
         <v>175</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J10" t="n">
         <v>175</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>43.32500076293945</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2077322525450171</v>
+        <v>0.2123643174414921</v>
       </c>
       <c r="J11" t="n">
         <v>147</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J12" t="n">
         <v>119</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="I13" t="n">
-        <v>4.166666666666666</v>
+        <v>4.159733618621054</v>
       </c>
       <c r="J13" t="n">
         <v>91</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.76200008392334</v>
+        <v>9.791000366210938</v>
       </c>
       <c r="I14" t="n">
-        <v>2.663388626969835</v>
+        <v>2.655499849609531</v>
       </c>
       <c r="J14" t="n">
         <v>84</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.39999961853027</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="I15" t="n">
-        <v>3.658536670464694</v>
+        <v>3.717472259539343</v>
       </c>
       <c r="J15" t="n">
         <v>84</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3.740000009536743</v>
+        <v>3.736000061035156</v>
       </c>
       <c r="I16" t="n">
-        <v>5.882352926176875</v>
+        <v>5.888650867394345</v>
       </c>
       <c r="J16" t="n">
         <v>84</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4799999892711639</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8620689903229801</v>
+        <v>0.8333333519597853</v>
       </c>
       <c r="J17" t="n">
         <v>84</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.96999979019165</v>
+        <v>6.005000114440918</v>
       </c>
       <c r="I18" t="n">
-        <v>4.020100643794084</v>
+        <v>3.99666936596461</v>
       </c>
       <c r="J18" t="n">
         <v>84</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>18.25</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="I19" t="n">
-        <v>2.06027397260274</v>
+        <v>2.06593397933063</v>
       </c>
       <c r="J19" t="n">
         <v>84</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.53000020980835</v>
+        <v>5.489999771118164</v>
       </c>
       <c r="I20" t="n">
-        <v>2.16998183448819</v>
+        <v>2.18579244085395</v>
       </c>
       <c r="J20" t="n">
         <v>77</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.25</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I23" t="n">
-        <v>1.647058823529412</v>
+        <v>1.666666742355108</v>
       </c>
       <c r="J23" t="n">
         <v>70</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>34.29999923706055</v>
+        <v>34.25</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4373177939838775</v>
+        <v>0.437956204379562</v>
       </c>
       <c r="J24" t="n">
         <v>70</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.300000190734863</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6349206156981752</v>
+        <v>0.6504064939792525</v>
       </c>
       <c r="J25" t="n">
         <v>63</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>22.6200008392334</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>1.105216581452932</v>
+        <v>1.096491264761248</v>
       </c>
       <c r="J26" t="n">
         <v>56</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>26.04999923706055</v>
+        <v>26</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7485604825760586</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="J27" t="n">
         <v>56</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.970000028610229</v>
+        <v>1.940000057220459</v>
       </c>
       <c r="I28" t="n">
-        <v>1.675126879225501</v>
+        <v>1.701030877663006</v>
       </c>
       <c r="J28" t="n">
         <v>56</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4.938000202178955</v>
+        <v>4.986000061035156</v>
       </c>
       <c r="I29" t="n">
-        <v>5.872822764811427</v>
+        <v>5.816285528480165</v>
       </c>
       <c r="J29" t="n">
         <v>56</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4.10200023651123</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I30" t="n">
-        <v>3.900536098849197</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J30" t="n">
         <v>56</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.604000091552734</v>
+        <v>2.614000082015991</v>
       </c>
       <c r="I31" t="n">
-        <v>5.322580458027345</v>
+        <v>5.302218655368509</v>
       </c>
       <c r="J31" t="n">
         <v>56</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>52.4900016784668</v>
+        <v>52.54000091552734</v>
       </c>
       <c r="I32" t="n">
-        <v>1.200228576594707</v>
+        <v>1.199086389459529</v>
       </c>
       <c r="J32" t="n">
         <v>56</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.114999771118164</v>
+        <v>5.105000019073486</v>
       </c>
       <c r="I33" t="n">
-        <v>2.737048020813407</v>
+        <v>2.742409392300234</v>
       </c>
       <c r="J33" t="n">
         <v>56</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>19</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="I34" t="n">
-        <v>4.105263157894737</v>
+        <v>4.06249983857076</v>
       </c>
       <c r="J34" t="n">
         <v>56</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>22.20000076293945</v>
+        <v>22.22999954223633</v>
       </c>
       <c r="I35" t="n">
-        <v>3.828828697244843</v>
+        <v>3.823661797136008</v>
       </c>
       <c r="J35" t="n">
         <v>56</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>43.33000183105469</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2077082764753009</v>
+        <v>0.2123643174414921</v>
       </c>
       <c r="J36" t="n">
         <v>56</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>6.650000095367432</v>
+        <v>6.679999828338623</v>
       </c>
       <c r="I37" t="n">
-        <v>2.726315750375679</v>
+        <v>2.714071926033133</v>
       </c>
       <c r="J37" t="n">
         <v>56</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>8.470000267028809</v>
+        <v>8.489999771118164</v>
       </c>
       <c r="I38" t="n">
-        <v>3.069657518336837</v>
+        <v>3.062426466541083</v>
       </c>
       <c r="J38" t="n">
         <v>56</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10.17000007629395</v>
+        <v>10.14999961853027</v>
       </c>
       <c r="I39" t="n">
-        <v>2.723697128043107</v>
+        <v>2.729064141975897</v>
       </c>
       <c r="J39" t="n">
         <v>56</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1.210000038146973</v>
+        <v>1.205000042915344</v>
       </c>
       <c r="I40" t="n">
-        <v>1.115702444164735</v>
+        <v>1.120331910307527</v>
       </c>
       <c r="J40" t="n">
         <v>49</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3.967999935150146</v>
+        <v>4.032000064849854</v>
       </c>
       <c r="I41" t="n">
-        <v>2.772177464661115</v>
+        <v>2.728174559295208</v>
       </c>
       <c r="J41" t="n">
         <v>49</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3.424999952316284</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="I43" t="n">
-        <v>4.671532911753591</v>
+        <v>4.664722941281676</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.14999961853027</v>
+        <v>28.39999961853027</v>
       </c>
       <c r="I45" t="n">
-        <v>3.943161687538076</v>
+        <v>3.90845075672379</v>
       </c>
       <c r="J45" t="n">
         <v>38</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9039999842643738</v>
+        <v>0.9160000085830688</v>
       </c>
       <c r="I46" t="n">
-        <v>3.318584128561946</v>
+        <v>3.275109139617372</v>
       </c>
       <c r="J46" t="n">
         <v>35</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5180000066757202</v>
       </c>
       <c r="I47" t="n">
-        <v>4.509804005899691</v>
+        <v>4.440154382931992</v>
       </c>
       <c r="J47" t="n">
         <v>35</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>18.95000076293945</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I48" t="n">
-        <v>3.166226785454389</v>
+        <v>3.191489491218789</v>
       </c>
       <c r="J48" t="n">
         <v>35</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.119999885559082</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I49" t="n">
-        <v>2.192982483658655</v>
+        <v>2.207505416522502</v>
       </c>
       <c r="J49" t="n">
         <v>35</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.585000038146973</v>
+        <v>2.555000066757202</v>
       </c>
       <c r="I50" t="n">
-        <v>6.96324941368399</v>
+        <v>7.045009600663354</v>
       </c>
       <c r="J50" t="n">
         <v>28</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8.600000381469727</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I51" t="n">
-        <v>3.488371938289734</v>
+        <v>3.571428733618088</v>
       </c>
       <c r="J51" t="n">
         <v>28</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>13.02999973297119</v>
+        <v>13.0600004196167</v>
       </c>
       <c r="I52" t="n">
-        <v>1.918649310232896</v>
+        <v>1.914241898679336</v>
       </c>
       <c r="J52" t="n">
         <v>28</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>3.299999952316284</v>
+        <v>3.309999942779541</v>
       </c>
       <c r="I53" t="n">
-        <v>0.909090922226919</v>
+        <v>0.9063444265442429</v>
       </c>
       <c r="J53" t="n">
         <v>28</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>3.730000019073486</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I54" t="n">
-        <v>4.02144770061581</v>
+        <v>3.968253998289063</v>
       </c>
       <c r="J54" t="n">
         <v>28</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>13.69999980926514</v>
+        <v>13.75</v>
       </c>
       <c r="I55" t="n">
-        <v>4.233576701276691</v>
+        <v>4.218181818181818</v>
       </c>
       <c r="J55" t="n">
         <v>28</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.401999950408936</v>
+        <v>2.392999887466431</v>
       </c>
       <c r="I56" t="n">
-        <v>4.329725318366231</v>
+        <v>4.346009397857062</v>
       </c>
       <c r="J56" t="n">
         <v>21</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>9.571999549865723</v>
+        <v>9.645999908447266</v>
       </c>
       <c r="I57" t="n">
-        <v>3.029670012929202</v>
+        <v>3.00642756326422</v>
       </c>
       <c r="J57" t="n">
         <v>21</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>38</v>
+        <v>38.20999908447266</v>
       </c>
       <c r="I59" t="n">
-        <v>4.315789473684211</v>
+        <v>4.292070241546916</v>
       </c>
       <c r="J59" t="n">
         <v>21</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>37.13999938964844</v>
+        <v>36.88000106811523</v>
       </c>
       <c r="I60" t="n">
-        <v>5.385029706159432</v>
+        <v>5.422993335347566</v>
       </c>
       <c r="J60" t="n">
         <v>21</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3.982000112533569</v>
+        <v>3.914000034332275</v>
       </c>
       <c r="I61" t="n">
-        <v>2.511300782871512</v>
+        <v>2.55493099445156</v>
       </c>
       <c r="J61" t="n">
         <v>21</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>31.31999969482422</v>
+        <v>30.97999954223633</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4740102217323257</v>
+        <v>0.4792124021745006</v>
       </c>
       <c r="J62" t="n">
         <v>21</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>23</v>
+        <v>23.07999992370605</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>3.986135195152426</v>
       </c>
       <c r="J63" t="n">
         <v>21</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>8.265000343322754</v>
+        <v>8.199999809265137</v>
       </c>
       <c r="I64" t="n">
-        <v>3.629763914557708</v>
+        <v>3.658536670464694</v>
       </c>
       <c r="J64" t="n">
         <v>21</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>83.83999633789062</v>
+        <v>83.45999908447266</v>
       </c>
       <c r="I65" t="n">
-        <v>1.240458069450061</v>
+        <v>1.246105932672466</v>
       </c>
       <c r="J65" t="n">
         <v>21</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>47.45000076293945</v>
+        <v>47.04999923706055</v>
       </c>
       <c r="I66" t="n">
-        <v>1.475237067955394</v>
+        <v>1.487778982679815</v>
       </c>
       <c r="J66" t="n">
         <v>21</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>55.79999923706055</v>
+        <v>56.25</v>
       </c>
       <c r="I67" t="n">
-        <v>3.942652383656005</v>
+        <v>3.911111111111112</v>
       </c>
       <c r="J67" t="n">
         <v>21</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>8.958000183105469</v>
+        <v>9.027999877929688</v>
       </c>
       <c r="I68" t="n">
-        <v>9.6003570263588</v>
+        <v>9.525919490787768</v>
       </c>
       <c r="J68" t="n">
         <v>21</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>12.05200004577637</v>
+        <v>12.19600009918213</v>
       </c>
       <c r="I69" t="n">
-        <v>4.646531678335435</v>
+        <v>4.591669362462157</v>
       </c>
       <c r="J69" t="n">
         <v>21</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>2.200000047683716</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I70" t="n">
-        <v>1.81818177877379</v>
+        <v>1.826483970542351</v>
       </c>
       <c r="J70" t="n">
         <v>21</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>9.5</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="I71" t="n">
-        <v>3.157894736842105</v>
+        <v>3.215434109894765</v>
       </c>
       <c r="J71" t="n">
         <v>21</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2.25</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>4.886877743701542</v>
       </c>
       <c r="J72" t="n">
         <v>21</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>72.30000305175781</v>
+        <v>72.90000152587891</v>
       </c>
       <c r="I73" t="n">
-        <v>2.849239160509158</v>
+        <v>2.825788692567746</v>
       </c>
       <c r="J73" t="n">
         <v>21</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>15.19999980926514</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="I74" t="n">
-        <v>4.934210588231973</v>
+        <v>4.966887291740587</v>
       </c>
       <c r="J74" t="n">
         <v>21</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>15.5</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="I75" t="n">
-        <v>1.935483870967742</v>
+        <v>1.948051996306679</v>
       </c>
       <c r="J75" t="n">
         <v>21</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>45.29999923706055</v>
+        <v>45.70000076293945</v>
       </c>
       <c r="I76" t="n">
-        <v>1.876379722551084</v>
+        <v>1.859956205272779</v>
       </c>
       <c r="J76" t="n">
         <v>21</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>33.91999816894531</v>
+        <v>34.13999938964844</v>
       </c>
       <c r="I77" t="n">
-        <v>2.505896361687302</v>
+        <v>2.489748140586458</v>
       </c>
       <c r="J77" t="n">
         <v>21</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>59.84000015258789</v>
+        <v>59.81999969482422</v>
       </c>
       <c r="I78" t="n">
-        <v>2.172459887508505</v>
+        <v>2.173186236429351</v>
       </c>
       <c r="J78" t="n">
         <v>21</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>8.119999885559082</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I79" t="n">
-        <v>7.389162665717064</v>
+        <v>7.334963051533854</v>
       </c>
       <c r="J79" t="n">
         <v>21</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>6</v>
+        <v>5.949999809265137</v>
       </c>
       <c r="I80" t="n">
-        <v>7.833333333333332</v>
+        <v>7.899159917083225</v>
       </c>
       <c r="J80" t="n">
         <v>21</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>6</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I81" t="n">
-        <v>3.333333333333333</v>
+        <v>3.367003334568775</v>
       </c>
       <c r="J81" t="n">
         <v>21</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>22.89999961853027</v>
+        <v>22.26000022888184</v>
       </c>
       <c r="I82" t="n">
-        <v>4.366812299816886</v>
+        <v>4.492362936737634</v>
       </c>
       <c r="J82" t="n">
         <v>21</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>4.800000190734863</v>
+        <v>4.730000019073486</v>
       </c>
       <c r="I83" t="n">
-        <v>4.479166488680582</v>
+        <v>4.545454527125229</v>
       </c>
       <c r="J83" t="n">
         <v>21</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>23.11499977111816</v>
+        <v>23.0049991607666</v>
       </c>
       <c r="I84" t="n">
-        <v>1.168072691643981</v>
+        <v>1.173657943272025</v>
       </c>
       <c r="J84" t="n">
         <v>21</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>8.199999809265137</v>
+        <v>8.460000038146973</v>
       </c>
       <c r="I85" t="n">
-        <v>2.439024446976463</v>
+        <v>2.364066183193621</v>
       </c>
       <c r="J85" t="n">
         <v>21</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>9.385000228881836</v>
+        <v>9.345000267028809</v>
       </c>
       <c r="I86" t="n">
-        <v>2.557272180573985</v>
+        <v>2.568218225169796</v>
       </c>
       <c r="J86" t="n">
         <v>21</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>21.02000045776367</v>
+        <v>21.23999977111816</v>
       </c>
       <c r="I87" t="n">
-        <v>3.758325322529743</v>
+        <v>3.719397403545316</v>
       </c>
       <c r="J87" t="n">
         <v>21</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>5.019999980926514</v>
       </c>
       <c r="I88" t="n">
-        <v>1.86</v>
+        <v>1.852589648473176</v>
       </c>
       <c r="J88" t="n">
         <v>21</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>5.699999809265137</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I89" t="n">
-        <v>1.052631614170798</v>
+        <v>1.034482724601393</v>
       </c>
       <c r="J89" t="n">
         <v>21</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>36.54000091552734</v>
+        <v>36.63999938964844</v>
       </c>
       <c r="I90" t="n">
-        <v>0.957854382130764</v>
+        <v>0.9552401905849437</v>
       </c>
       <c r="J90" t="n">
         <v>21</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>7.275000095367432</v>
+        <v>7.289999961853027</v>
       </c>
       <c r="I91" t="n">
-        <v>7.619243886374197</v>
+        <v>7.603566569280254</v>
       </c>
       <c r="J91" t="n">
         <v>21</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>2.170000076293945</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I92" t="n">
-        <v>2.764976861312906</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J92" t="n">
         <v>21</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>12.75</v>
+        <v>12.85000038146973</v>
       </c>
       <c r="I93" t="n">
-        <v>1.568627450980392</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J93" t="n">
         <v>21</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>6.110000133514404</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I94" t="n">
-        <v>1.685761010626289</v>
+        <v>1.680260980050472</v>
       </c>
       <c r="J94" t="n">
         <v>21</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>5.673999786376953</v>
+        <v>5.671000003814697</v>
       </c>
       <c r="I95" t="n">
-        <v>3.348607810246705</v>
+        <v>3.350379119594307</v>
       </c>
       <c r="J95" t="n">
         <v>21</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>10.28499984741211</v>
+        <v>10.26000022888184</v>
       </c>
       <c r="I96" t="n">
-        <v>4.20029174923808</v>
+        <v>4.210526221860334</v>
       </c>
       <c r="J96" t="n">
         <v>21</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>26.48999977111816</v>
+        <v>26.03000068664551</v>
       </c>
       <c r="I97" t="n">
-        <v>1.661004166861974</v>
+        <v>1.690357235471525</v>
       </c>
       <c r="J97" t="n">
         <v>21</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>8.479999542236328</v>
+        <v>8.369999885559082</v>
       </c>
       <c r="I99" t="n">
-        <v>5.542453129378973</v>
+        <v>5.6152927888434</v>
       </c>
       <c r="J99" t="n">
         <v>21</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>54.72000122070312</v>
+        <v>54.97999954223633</v>
       </c>
       <c r="I100" t="n">
-        <v>2.558479475088745</v>
+        <v>2.546380523201901</v>
       </c>
       <c r="J100" t="n">
         <v>21</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>3.746000051498413</v>
+        <v>3.871999979019165</v>
       </c>
       <c r="I101" t="n">
-        <v>8.00854233517693</v>
+        <v>7.747933926280506</v>
       </c>
       <c r="J101" t="n">
         <v>21</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3.539999961853027</v>
+        <v>3.569999933242798</v>
       </c>
       <c r="I103" t="n">
-        <v>4.802259938754712</v>
+        <v>4.761904850949985</v>
       </c>
       <c r="J103" t="n">
         <v>21</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>20.54999923706055</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="I104" t="n">
-        <v>3.406326160526551</v>
+        <v>3.531786129052249</v>
       </c>
       <c r="J104" t="n">
         <v>21</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>2.680000066757202</v>
+        <v>2.700000047683716</v>
       </c>
       <c r="I105" t="n">
-        <v>1.305970116722794</v>
+        <v>1.29629627340288</v>
       </c>
       <c r="J105" t="n">
         <v>21</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>6.150000095367432</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I106" t="n">
-        <v>5.365853575328834</v>
+        <v>5.383360421520929</v>
       </c>
       <c r="J106" t="n">
         <v>21</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.9850000143051147</v>
+        <v>0.9869999885559082</v>
       </c>
       <c r="I107" t="n">
-        <v>7.106598881562729</v>
+        <v>7.092198663793084</v>
       </c>
       <c r="J107" t="n">
         <v>21</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>49.86000061035156</v>
+        <v>49.7599983215332</v>
       </c>
       <c r="I108" t="n">
-        <v>1.423987146627903</v>
+        <v>1.426848922727463</v>
       </c>
       <c r="J108" t="n">
         <v>21</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>91.65000152587891</v>
+        <v>91.44999694824219</v>
       </c>
       <c r="I109" t="n">
-        <v>1.472995065492503</v>
+        <v>1.476216561017555</v>
       </c>
       <c r="J109" t="n">
         <v>21</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>7.199999809265137</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="I110" t="n">
-        <v>1.111111140545505</v>
+        <v>1.114206154772446</v>
       </c>
       <c r="J110" t="n">
         <v>21</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>4.557000160217285</v>
+        <v>4.521999835968018</v>
       </c>
       <c r="I112" t="n">
-        <v>3.730524336692017</v>
+        <v>3.759398632609821</v>
       </c>
       <c r="J112" t="n">
         <v>21</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>7.900000095367432</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I113" t="n">
-        <v>3.75949362550212</v>
+        <v>3.907894785879722</v>
       </c>
       <c r="J113" t="n">
         <v>21</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>59.40000152587891</v>
+        <v>59.5</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7575757381150027</v>
+        <v>0.7563025210084033</v>
       </c>
       <c r="J114" t="n">
         <v>21</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>4.659999847412109</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8583691268190417</v>
+        <v>0.8474576647889183</v>
       </c>
       <c r="J115" t="n">
         <v>21</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>33.61999893188477</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="I116" t="n">
-        <v>3.123141086730356</v>
+        <v>3.125000141915828</v>
       </c>
       <c r="J116" t="n">
         <v>21</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>19.93000030517578</v>
+        <v>20.18000030517578</v>
       </c>
       <c r="I118" t="n">
-        <v>1.906673327552909</v>
+        <v>1.883052498777898</v>
       </c>
       <c r="J118" t="n">
         <v>21</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>27.31999969482422</v>
+        <v>26.8700008392334</v>
       </c>
       <c r="I119" t="n">
-        <v>2.196193289539714</v>
+        <v>2.23297350673666</v>
       </c>
       <c r="J119" t="n">
         <v>21</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>35.65000152587891</v>
+        <v>35.5</v>
       </c>
       <c r="I120" t="n">
-        <v>0.9817671389044105</v>
+        <v>0.9859154929577464</v>
       </c>
       <c r="J120" t="n">
         <v>21</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>3.400000095367432</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I121" t="n">
-        <v>0.4999999859753781</v>
+        <v>0.488505744448992</v>
       </c>
       <c r="J121" t="n">
         <v>21</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>2.859999895095825</v>
+        <v>2.890000104904175</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3496503624754485</v>
+        <v>0.3460207486854598</v>
       </c>
       <c r="J122" t="n">
         <v>21</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>22.04999923706055</v>
+        <v>22.09000015258789</v>
       </c>
       <c r="I123" t="n">
-        <v>5.079365255113295</v>
+        <v>5.070167461582338</v>
       </c>
       <c r="J123" t="n">
         <v>21</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>1.470000028610229</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I124" t="n">
-        <v>6.802720956035778</v>
+        <v>6.711409353016787</v>
       </c>
       <c r="J124" t="n">
         <v>21</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>2.371999979019165</v>
+        <v>2.335999965667725</v>
       </c>
       <c r="I126" t="n">
-        <v>3.891231063086541</v>
+        <v>3.951198688207894</v>
       </c>
       <c r="J126" t="n">
         <v>21</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>9.220000267028809</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I127" t="n">
-        <v>3.796095334743296</v>
+        <v>3.645833188460938</v>
       </c>
       <c r="J127" t="n">
         <v>14</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5.349999904632568</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I128" t="n">
-        <v>1.794392555350768</v>
+        <v>1.761467951554743</v>
       </c>
       <c r="J128" t="n">
         <v>14</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>11.60000038146973</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I130" t="n">
-        <v>1.724137874335655</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J130" t="n">
         <v>14</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>9.399999618530273</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="I131" t="n">
-        <v>0.6382978982437579</v>
+        <v>0.6329114229666515</v>
       </c>
       <c r="J131" t="n">
         <v>14</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>16.02000045776367</v>
+        <v>16.34000015258789</v>
       </c>
       <c r="I133" t="n">
-        <v>3.121098537532739</v>
+        <v>3.059975491620857</v>
       </c>
       <c r="J133" t="n">
         <v>14</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.980000019073486</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I135" t="n">
-        <v>3.691275144159233</v>
+        <v>3.61842109803678</v>
       </c>
       <c r="J135" t="n">
         <v>14</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.649999618530273</v>
+        <v>9.399999618530273</v>
       </c>
       <c r="I136" t="n">
-        <v>0.880829050363691</v>
+        <v>0.9042553558453239</v>
       </c>
       <c r="J136" t="n">
         <v>14</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4.889999866485596</v>
+        <v>4.880000114440918</v>
       </c>
       <c r="I137" t="n">
-        <v>1.942740339342294</v>
+        <v>1.946721265822835</v>
       </c>
       <c r="J137" t="n">
         <v>14</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>7.090000152587891</v>
+        <v>7</v>
       </c>
       <c r="I141" t="n">
-        <v>3.102961851414047</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="J141" t="n">
         <v>14</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>25.70000076293945</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="I142" t="n">
-        <v>2.373540785569342</v>
+        <v>2.406311600870413</v>
       </c>
       <c r="J142" t="n">
         <v>7</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>3.029999971389771</v>
+        <v>3.059999942779541</v>
       </c>
       <c r="I143" t="n">
-        <v>4.950495096249109</v>
+        <v>4.901960875977926</v>
       </c>
       <c r="J143" t="n">
         <v>7</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>12.69999980926514</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I144" t="n">
-        <v>5.511811106401145</v>
+        <v>5.737705007736096</v>
       </c>
       <c r="J144" t="n">
         <v>7</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>9.289999961853027</v>
+        <v>9.229999542236328</v>
       </c>
       <c r="I145" t="n">
-        <v>5.495156104372827</v>
+        <v>5.530877847436072</v>
       </c>
       <c r="J145" t="n">
         <v>7</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>7.644999980926514</v>
+        <v>7.554999828338623</v>
       </c>
       <c r="I146" t="n">
-        <v>3.531720087293946</v>
+        <v>3.573792271804382</v>
       </c>
       <c r="J146" t="n">
         <v>7</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>5.809999942779541</v>
+        <v>5.710000038146973</v>
       </c>
       <c r="I147" t="n">
-        <v>6.024096444871181</v>
+        <v>6.129597156948235</v>
       </c>
       <c r="J147" t="n">
         <v>7</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>18.79999923706055</v>
+        <v>19</v>
       </c>
       <c r="I149" t="n">
-        <v>3.989361864023487</v>
+        <v>3.947368421052631</v>
       </c>
       <c r="J149" t="n">
         <v>7</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>11.55000019073486</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="I150" t="n">
-        <v>3.722943661463623</v>
+        <v>3.706896429821658</v>
       </c>
       <c r="J150" t="n">
         <v>7</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>4.304999828338623</v>
+        <v>4.295000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>3.484320696428174</v>
+        <v>3.49243299966205</v>
       </c>
       <c r="J151" t="n">
         <v>7</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>12.42000007629395</v>
+        <v>12.64000034332275</v>
       </c>
       <c r="I152" t="n">
-        <v>1.58751206754287</v>
+        <v>1.559881286745036</v>
       </c>
       <c r="J152" t="n">
         <v>7</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>28.95000076293945</v>
+        <v>29</v>
       </c>
       <c r="I153" t="n">
-        <v>3.799654476721717</v>
+        <v>3.793103448275863</v>
       </c>
       <c r="J153" t="n">
         <v>7</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>46.95000076293945</v>
+        <v>47</v>
       </c>
       <c r="I154" t="n">
-        <v>1.001064946458958</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
         <v>7</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>79.80000305175781</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="I155" t="n">
-        <v>1.503759340988605</v>
+        <v>1.524777695721121</v>
       </c>
       <c r="J155" t="n">
         <v>7</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>24</v>
+        <v>23.64999961853027</v>
       </c>
       <c r="I156" t="n">
-        <v>1.125</v>
+        <v>1.141649067040362</v>
       </c>
       <c r="J156" t="n">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>10.44999980926514</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I157" t="n">
-        <v>3.636363702735056</v>
+        <v>3.601895669478002</v>
       </c>
       <c r="J157" t="n">
         <v>7</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>30.10000038146973</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>0.996677728232479</v>
+        <v>1.01522845260771</v>
       </c>
       <c r="J158" t="n">
         <v>7</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>0.1896000057458878</v>
+        <v>0.1876000016927719</v>
       </c>
       <c r="I159" t="n">
-        <v>3.69198301047616</v>
+        <v>3.731343249913043</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>7.289999961853027</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="I160" t="n">
-        <v>2.194787391457407</v>
+        <v>2.256699528301126</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>2.174999952316284</v>
+        <v>2.170000076293945</v>
       </c>
       <c r="I161" t="n">
-        <v>2.988505812645086</v>
+        <v>2.995391599755649</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>7.639999866485596</v>
+        <v>7.659999847412109</v>
       </c>
       <c r="I162" t="n">
-        <v>3.272251366085431</v>
+        <v>3.263707636814917</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>1.399999976158142</v>
+        <v>1.419999957084656</v>
       </c>
       <c r="I163" t="n">
-        <v>5.000000085149495</v>
+        <v>4.929577613770789</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>6.510000228881836</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="I164" t="n">
-        <v>7.680491281424739</v>
+        <v>7.518796884654384</v>
       </c>
       <c r="J164" t="n">
         <v>-7</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>18.43499946594238</v>
+        <v>18.61000061035156</v>
       </c>
       <c r="I165" t="n">
-        <v>3.525901919340102</v>
+        <v>3.492745721020805</v>
       </c>
       <c r="J165" t="n">
         <v>-7</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>12.32499980926514</v>
+        <v>12.36499977111816</v>
       </c>
       <c r="I166" t="n">
-        <v>4.381338810196678</v>
+        <v>4.367165467008884</v>
       </c>
       <c r="J166" t="n">
         <v>-7</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.185999870300293</v>
+        <v>6.216000080108643</v>
       </c>
       <c r="I167" t="n">
-        <v>1.616553541814827</v>
+        <v>1.608751588018838</v>
       </c>
       <c r="J167" t="n">
         <v>-7</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>9.220000267028809</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I168" t="n">
-        <v>1.735357867311221</v>
+        <v>1.731601774494826</v>
       </c>
       <c r="J168" t="n">
         <v>-7</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>297.75</v>
+        <v>296.1000061035156</v>
       </c>
       <c r="I169" t="n">
-        <v>1.214105793450882</v>
+        <v>1.22087130208846</v>
       </c>
       <c r="J169" t="n">
         <v>-7</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>29.39999961853027</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="I170" t="n">
-        <v>4.625850400157208</v>
+        <v>4.5945945353818</v>
       </c>
       <c r="J170" t="n">
         <v>-7</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>14.85000038146973</v>
+        <v>14.67000007629395</v>
       </c>
       <c r="I172" t="n">
-        <v>3.939393838198014</v>
+        <v>3.987730040610794</v>
       </c>
       <c r="J172" t="n">
         <v>-7</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>19.55999946594238</v>
+        <v>19.69000053405762</v>
       </c>
       <c r="I173" t="n">
-        <v>3.220858983646435</v>
+        <v>3.199593615603487</v>
       </c>
       <c r="J173" t="n">
         <v>-7</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>126.8499984741211</v>
+        <v>124.5500030517578</v>
       </c>
       <c r="I174" t="n">
-        <v>0.7094994172850626</v>
+        <v>0.7226013472083156</v>
       </c>
       <c r="J174" t="n">
         <v>-7</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>64.5</v>
+        <v>64.38999938964844</v>
       </c>
       <c r="I175" t="n">
-        <v>2.667906976744186</v>
+        <v>2.672464693759016</v>
       </c>
       <c r="J175" t="n">
         <v>-7</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>25.89999961853027</v>
+        <v>26</v>
       </c>
       <c r="I176" t="n">
-        <v>0.540540548501925</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="J176" t="n">
         <v>-14</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>2.099999904632568</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I178" t="n">
-        <v>1.619047692573534</v>
+        <v>1.588784968845712</v>
       </c>
       <c r="J178" t="n">
         <v>-28</v>
@@ -9402,7 +9402,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9419,7 +9419,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9429,14 +9429,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9810,7 +9810,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9861,7 +9861,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9878,7 +9878,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10048,7 +10048,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10082,7 +10082,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10092,14 +10092,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10116,7 +10116,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10133,7 +10133,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10150,7 +10150,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10167,7 +10167,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10184,7 +10184,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10201,7 +10201,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10211,14 +10211,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10235,7 +10235,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10252,7 +10252,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10262,14 +10262,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10286,7 +10286,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10303,7 +10303,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10320,7 +10320,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10337,7 +10337,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10354,7 +10354,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10371,7 +10371,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10381,14 +10381,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10405,7 +10405,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10422,7 +10422,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10439,7 +10439,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10456,7 +10456,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10466,14 +10466,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10483,14 +10483,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10524,7 +10524,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10541,7 +10541,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10551,14 +10551,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10568,14 +10568,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10592,7 +10592,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10609,7 +10609,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10626,7 +10626,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10643,7 +10643,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10660,7 +10660,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10677,7 +10677,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10687,14 +10687,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10711,7 +10711,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10728,7 +10728,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10745,7 +10745,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10762,7 +10762,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10779,7 +10779,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10796,7 +10796,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10813,7 +10813,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10830,7 +10830,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10847,7 +10847,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10864,7 +10864,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10881,7 +10881,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10898,7 +10898,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10915,7 +10915,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10932,7 +10932,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10949,7 +10949,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10966,7 +10966,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10983,7 +10983,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11000,7 +11000,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11027,14 +11027,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11051,7 +11051,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11068,7 +11068,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11085,7 +11085,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11095,14 +11095,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11119,7 +11119,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11136,7 +11136,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11153,7 +11153,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11163,14 +11163,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11221,7 +11221,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11231,14 +11231,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11248,14 +11248,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11272,7 +11272,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11282,14 +11282,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11306,7 +11306,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11323,7 +11323,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11340,7 +11340,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11357,7 +11357,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11367,14 +11367,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11384,14 +11384,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11408,7 +11408,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11418,14 +11418,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11442,7 +11442,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11476,7 +11476,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11493,7 +11493,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11510,7 +11510,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11527,7 +11527,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11537,14 +11537,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11561,7 +11561,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11578,7 +11578,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11588,14 +11588,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11605,14 +11605,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11629,7 +11629,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11646,7 +11646,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11663,7 +11663,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11680,7 +11680,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11697,7 +11697,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11714,7 +11714,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11724,14 +11724,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11748,7 +11748,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11758,14 +11758,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11775,14 +11775,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11799,7 +11799,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11816,7 +11816,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11826,14 +11826,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11843,14 +11843,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11867,7 +11867,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11884,7 +11884,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11901,7 +11901,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11935,7 +11935,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11952,7 +11952,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11969,7 +11969,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11986,7 +11986,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12003,7 +12003,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12020,7 +12020,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12037,7 +12037,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12054,7 +12054,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12071,7 +12071,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12088,7 +12088,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12105,7 +12105,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12122,7 +12122,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12156,7 +12156,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12166,14 +12166,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12183,14 +12183,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12217,14 +12217,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12234,14 +12234,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12258,7 +12258,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12268,14 +12268,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12292,7 +12292,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12309,7 +12309,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12326,7 +12326,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12343,7 +12343,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12360,7 +12360,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12377,7 +12377,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12394,7 +12394,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12411,7 +12411,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12428,7 +12428,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12445,7 +12445,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12462,7 +12462,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12479,7 +12479,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12496,7 +12496,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12506,14 +12506,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12523,14 +12523,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12547,7 +12547,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12557,14 +12557,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12581,7 +12581,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12598,7 +12598,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12615,7 +12615,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12625,14 +12625,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12642,14 +12642,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12659,14 +12659,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12683,7 +12683,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12693,14 +12693,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12717,7 +12717,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12734,7 +12734,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12751,7 +12751,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12768,7 +12768,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12785,7 +12785,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12802,7 +12802,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12812,14 +12812,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12836,7 +12836,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12853,7 +12853,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12870,7 +12870,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12887,7 +12887,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12904,7 +12904,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12921,7 +12921,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12938,7 +12938,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12955,7 +12955,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12972,7 +12972,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12982,14 +12982,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12999,14 +12999,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13023,7 +13023,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13033,14 +13033,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13057,7 +13057,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13074,7 +13074,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13091,7 +13091,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13101,14 +13101,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13125,7 +13125,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13142,7 +13142,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13159,7 +13159,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13176,7 +13176,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13186,14 +13186,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13227,7 +13227,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13237,14 +13237,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13261,7 +13261,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13278,7 +13278,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13288,14 +13288,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13312,7 +13312,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13329,7 +13329,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13339,7 +13339,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13363,7 +13363,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13380,7 +13380,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13390,14 +13390,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13414,7 +13414,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13431,7 +13431,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13441,14 +13441,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13465,7 +13465,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13482,7 +13482,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13499,7 +13499,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13509,14 +13509,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13550,7 +13550,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13560,14 +13560,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13577,14 +13577,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13611,14 +13611,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13628,14 +13628,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13645,14 +13645,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13662,14 +13662,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13686,7 +13686,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13696,14 +13696,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13737,7 +13737,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13747,14 +13747,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13781,14 +13781,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13805,7 +13805,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13815,14 +13815,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13832,14 +13832,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13849,14 +13849,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13873,7 +13873,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13907,7 +13907,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13924,7 +13924,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13975,7 +13975,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13985,14 +13985,14 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14009,7 +14009,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14019,14 +14019,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14036,14 +14036,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14077,7 +14077,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14094,7 +14094,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14104,14 +14104,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14121,14 +14121,14 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14138,14 +14138,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14155,14 +14155,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14179,7 +14179,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14189,14 +14189,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14206,14 +14206,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14230,7 +14230,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14240,14 +14240,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14257,14 +14257,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14281,7 +14281,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14298,7 +14298,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14315,7 +14315,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14325,14 +14325,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14342,14 +14342,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14359,14 +14359,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14383,7 +14383,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14393,14 +14393,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14410,14 +14410,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14434,7 +14434,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14451,7 +14451,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14461,14 +14461,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14485,7 +14485,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14495,14 +14495,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14512,14 +14512,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14529,14 +14529,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14553,7 +14553,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14563,14 +14563,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14580,14 +14580,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14597,14 +14597,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14614,14 +14614,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14631,14 +14631,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14655,7 +14655,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14672,7 +14672,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14682,14 +14682,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14699,14 +14699,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14716,14 +14716,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14733,14 +14733,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14791,7 +14791,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14818,14 +14818,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14835,14 +14835,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14859,7 +14859,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14876,7 +14876,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14893,7 +14893,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14903,14 +14903,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14927,7 +14927,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14944,7 +14944,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14954,14 +14954,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14971,14 +14971,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -15005,14 +15005,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15022,14 +15022,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15039,14 +15039,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15063,7 +15063,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15080,7 +15080,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15097,7 +15097,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15114,7 +15114,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15131,7 +15131,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15141,14 +15141,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15158,14 +15158,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15175,14 +15175,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15192,14 +15192,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15216,7 +15216,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15226,14 +15226,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15243,14 +15243,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15260,14 +15260,14 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15277,14 +15277,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15301,7 +15301,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15311,14 +15311,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15328,14 +15328,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15345,14 +15345,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15362,14 +15362,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15386,7 +15386,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15403,7 +15403,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15413,14 +15413,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15437,7 +15437,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15471,7 +15471,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15522,7 +15522,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15539,7 +15539,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15549,14 +15549,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15566,14 +15566,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15583,14 +15583,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15607,7 +15607,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15624,7 +15624,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15641,7 +15641,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15651,14 +15651,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15675,7 +15675,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15692,7 +15692,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15702,14 +15702,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15719,14 +15719,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15736,14 +15736,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15753,14 +15753,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15804,14 +15804,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15828,7 +15828,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15838,14 +15838,14 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15862,7 +15862,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15872,14 +15872,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15889,14 +15889,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15906,14 +15906,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15930,7 +15930,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15947,7 +15947,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15964,7 +15964,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15974,14 +15974,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15998,7 +15998,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -16015,7 +16015,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -16025,14 +16025,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16042,14 +16042,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16083,7 +16083,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16100,7 +16100,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16110,14 +16110,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16134,7 +16134,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16151,7 +16151,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16161,14 +16161,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16178,14 +16178,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16212,14 +16212,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16229,14 +16229,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16246,14 +16246,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16263,14 +16263,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16287,7 +16287,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16304,7 +16304,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16321,7 +16321,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16338,7 +16338,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16355,7 +16355,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16372,7 +16372,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16389,7 +16389,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16399,14 +16399,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16416,14 +16416,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16433,14 +16433,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16450,14 +16450,14 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16474,7 +16474,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16491,7 +16491,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16501,14 +16501,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16518,14 +16518,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16535,14 +16535,14 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16552,14 +16552,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16576,7 +16576,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16593,7 +16593,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16610,7 +16610,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16627,7 +16627,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16637,14 +16637,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16654,14 +16654,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16671,14 +16671,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16695,7 +16695,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16712,7 +16712,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16729,7 +16729,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16746,7 +16746,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16763,7 +16763,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16780,7 +16780,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16790,14 +16790,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16807,14 +16807,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16824,14 +16824,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16841,14 +16841,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16865,7 +16865,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16882,7 +16882,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16892,14 +16892,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16926,14 +16926,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16943,14 +16943,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16967,7 +16967,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16984,7 +16984,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16994,14 +16994,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -17011,14 +17011,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -17035,7 +17035,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -17045,14 +17045,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -17069,7 +17069,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -17086,7 +17086,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17103,7 +17103,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17120,7 +17120,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17137,7 +17137,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17147,14 +17147,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17171,7 +17171,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17188,7 +17188,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17205,7 +17205,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17215,14 +17215,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17232,14 +17232,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17256,7 +17256,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17273,7 +17273,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17290,7 +17290,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17300,14 +17300,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17324,7 +17324,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17341,7 +17341,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17358,7 +17358,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17375,7 +17375,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17392,7 +17392,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17409,7 +17409,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17426,7 +17426,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17443,7 +17443,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17477,7 +17477,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17487,14 +17487,14 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17511,7 +17511,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17521,14 +17521,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17579,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17613,7 +17613,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -17647,7 +17647,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17657,14 +17657,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17681,7 +17681,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17698,7 +17698,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17708,14 +17708,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17742,14 +17742,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17766,7 +17766,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17783,7 +17783,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17800,7 +17800,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17817,7 +17817,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17834,7 +17834,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17851,7 +17851,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17861,14 +17861,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17902,7 +17902,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17919,7 +17919,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17936,7 +17936,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -18004,7 +18004,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18014,14 +18014,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18031,7 +18031,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -18055,7 +18055,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18065,14 +18065,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18082,14 +18082,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18099,14 +18099,14 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18116,14 +18116,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18133,14 +18133,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18157,7 +18157,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18167,14 +18167,14 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18184,14 +18184,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18201,14 +18201,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18218,14 +18218,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18235,14 +18235,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18252,14 +18252,14 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18269,14 +18269,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18286,14 +18286,14 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18303,14 +18303,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -18361,7 +18361,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18378,7 +18378,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18395,7 +18395,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18412,7 +18412,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18429,7 +18429,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18446,7 +18446,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18456,14 +18456,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18473,14 +18473,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18497,7 +18497,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18507,14 +18507,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18524,14 +18524,14 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18548,7 +18548,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18565,7 +18565,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18582,7 +18582,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18599,7 +18599,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18633,7 +18633,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18643,14 +18643,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18660,7 +18660,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -18692,146 +18692,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004093263</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-06-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>3.424999952316284</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.671532911753591</v>
-      </c>
-      <c r="I2" t="n">
-        <v>42</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005433765</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9200000166893005</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2.71739125505287</v>
-      </c>
-      <c r="I3" t="n">
-        <v>42</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18842,197 +18705,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEFFE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BFF Bank S.P.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MONDO TV FRANCE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>